--- a/artfynd/A 37027-2026 artfynd.xlsx
+++ b/artfynd/A 37027-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136348932</v>
       </c>
       <c r="B2" t="n">
-        <v>92281</v>
+        <v>92284</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136348931</v>
       </c>
       <c r="B8" t="n">
-        <v>93416</v>
+        <v>93419</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>136348925</v>
       </c>
       <c r="B9" t="n">
-        <v>93392</v>
+        <v>93395</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>136348926</v>
       </c>
       <c r="B10" t="n">
-        <v>93392</v>
+        <v>93395</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>136348930</v>
       </c>
       <c r="B11" t="n">
-        <v>93392</v>
+        <v>93395</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>136348927</v>
       </c>
       <c r="B12" t="n">
-        <v>93394</v>
+        <v>93397</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>136348929</v>
       </c>
       <c r="B13" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>136348936</v>
       </c>
       <c r="B14" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>136348937</v>
       </c>
       <c r="B15" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>136348928</v>
       </c>
       <c r="B16" t="n">
-        <v>93404</v>
+        <v>93407</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>136348933</v>
       </c>
       <c r="B17" t="n">
-        <v>93404</v>
+        <v>93407</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>136348934</v>
       </c>
       <c r="B19" t="n">
-        <v>93412</v>
+        <v>93415</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>136348935</v>
       </c>
       <c r="B20" t="n">
-        <v>93412</v>
+        <v>93415</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>136348940</v>
       </c>
       <c r="B21" t="n">
-        <v>93412</v>
+        <v>93415</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>136348939</v>
       </c>
       <c r="B22" t="n">
-        <v>93044</v>
+        <v>93047</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         <v>136348938</v>
       </c>
       <c r="B27" t="n">
-        <v>93438</v>
+        <v>93441</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 37027-2026 artfynd.xlsx
+++ b/artfynd/A 37027-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136348932</v>
       </c>
       <c r="B2" t="n">
-        <v>92284</v>
+        <v>92285</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136348931</v>
       </c>
       <c r="B8" t="n">
-        <v>93419</v>
+        <v>93420</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>136348925</v>
       </c>
       <c r="B9" t="n">
-        <v>93395</v>
+        <v>93396</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>136348926</v>
       </c>
       <c r="B10" t="n">
-        <v>93395</v>
+        <v>93396</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>136348930</v>
       </c>
       <c r="B11" t="n">
-        <v>93395</v>
+        <v>93396</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>136348927</v>
       </c>
       <c r="B12" t="n">
-        <v>93397</v>
+        <v>93398</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>136348929</v>
       </c>
       <c r="B13" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>136348936</v>
       </c>
       <c r="B14" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>136348937</v>
       </c>
       <c r="B15" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>136348928</v>
       </c>
       <c r="B16" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>136348933</v>
       </c>
       <c r="B17" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>136348934</v>
       </c>
       <c r="B19" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>136348935</v>
       </c>
       <c r="B20" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>136348940</v>
       </c>
       <c r="B21" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>136348939</v>
       </c>
       <c r="B22" t="n">
-        <v>93047</v>
+        <v>93048</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         <v>136348938</v>
       </c>
       <c r="B27" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 37027-2026 artfynd.xlsx
+++ b/artfynd/A 37027-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136348932</v>
       </c>
       <c r="B2" t="n">
-        <v>92285</v>
+        <v>92290</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136348931</v>
       </c>
       <c r="B8" t="n">
-        <v>93420</v>
+        <v>93425</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>136348925</v>
       </c>
       <c r="B9" t="n">
-        <v>93396</v>
+        <v>93401</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>136348926</v>
       </c>
       <c r="B10" t="n">
-        <v>93396</v>
+        <v>93401</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>136348930</v>
       </c>
       <c r="B11" t="n">
-        <v>93396</v>
+        <v>93401</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>136348927</v>
       </c>
       <c r="B12" t="n">
-        <v>93398</v>
+        <v>93403</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>136348929</v>
       </c>
       <c r="B13" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>136348936</v>
       </c>
       <c r="B14" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>136348937</v>
       </c>
       <c r="B15" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>136348928</v>
       </c>
       <c r="B16" t="n">
-        <v>93408</v>
+        <v>93413</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>136348933</v>
       </c>
       <c r="B17" t="n">
-        <v>93408</v>
+        <v>93413</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>136348934</v>
       </c>
       <c r="B19" t="n">
-        <v>93416</v>
+        <v>93421</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>136348935</v>
       </c>
       <c r="B20" t="n">
-        <v>93416</v>
+        <v>93421</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>136348940</v>
       </c>
       <c r="B21" t="n">
-        <v>93416</v>
+        <v>93421</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>136348939</v>
       </c>
       <c r="B22" t="n">
-        <v>93048</v>
+        <v>93053</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         <v>136348938</v>
       </c>
       <c r="B27" t="n">
-        <v>93442</v>
+        <v>93447</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 37027-2026 artfynd.xlsx
+++ b/artfynd/A 37027-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136348932</v>
       </c>
       <c r="B2" t="n">
-        <v>92290</v>
+        <v>92292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136348931</v>
       </c>
       <c r="B8" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>136348925</v>
       </c>
       <c r="B9" t="n">
-        <v>93401</v>
+        <v>93403</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>136348926</v>
       </c>
       <c r="B10" t="n">
-        <v>93401</v>
+        <v>93403</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>136348930</v>
       </c>
       <c r="B11" t="n">
-        <v>93401</v>
+        <v>93403</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>136348927</v>
       </c>
       <c r="B12" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>136348929</v>
       </c>
       <c r="B13" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>136348936</v>
       </c>
       <c r="B14" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>136348937</v>
       </c>
       <c r="B15" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>136348928</v>
       </c>
       <c r="B16" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>136348933</v>
       </c>
       <c r="B17" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>136348934</v>
       </c>
       <c r="B19" t="n">
-        <v>93421</v>
+        <v>93423</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>136348935</v>
       </c>
       <c r="B20" t="n">
-        <v>93421</v>
+        <v>93423</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>136348940</v>
       </c>
       <c r="B21" t="n">
-        <v>93421</v>
+        <v>93423</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>136348939</v>
       </c>
       <c r="B22" t="n">
-        <v>93053</v>
+        <v>93055</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         <v>136348938</v>
       </c>
       <c r="B27" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 37027-2026 artfynd.xlsx
+++ b/artfynd/A 37027-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136348932</v>
       </c>
       <c r="B2" t="n">
-        <v>92292</v>
+        <v>92294</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136348931</v>
       </c>
       <c r="B8" t="n">
-        <v>93427</v>
+        <v>93429</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>136348925</v>
       </c>
       <c r="B9" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>136348926</v>
       </c>
       <c r="B10" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>136348930</v>
       </c>
       <c r="B11" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>136348927</v>
       </c>
       <c r="B12" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>136348929</v>
       </c>
       <c r="B13" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>136348936</v>
       </c>
       <c r="B14" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>136348937</v>
       </c>
       <c r="B15" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>136348928</v>
       </c>
       <c r="B16" t="n">
-        <v>93415</v>
+        <v>93417</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>136348933</v>
       </c>
       <c r="B17" t="n">
-        <v>93415</v>
+        <v>93417</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>136348934</v>
       </c>
       <c r="B19" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>136348935</v>
       </c>
       <c r="B20" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>136348940</v>
       </c>
       <c r="B21" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>136348939</v>
       </c>
       <c r="B22" t="n">
-        <v>93055</v>
+        <v>93057</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         <v>136348938</v>
       </c>
       <c r="B27" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 37027-2026 artfynd.xlsx
+++ b/artfynd/A 37027-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136348932</v>
       </c>
       <c r="B2" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136348931</v>
       </c>
       <c r="B8" t="n">
-        <v>93429</v>
+        <v>93431</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>136348925</v>
       </c>
       <c r="B9" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>136348926</v>
       </c>
       <c r="B10" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>136348930</v>
       </c>
       <c r="B11" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>136348927</v>
       </c>
       <c r="B12" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>136348929</v>
       </c>
       <c r="B13" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>136348936</v>
       </c>
       <c r="B14" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>136348937</v>
       </c>
       <c r="B15" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>136348928</v>
       </c>
       <c r="B16" t="n">
-        <v>93417</v>
+        <v>93419</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>136348933</v>
       </c>
       <c r="B17" t="n">
-        <v>93417</v>
+        <v>93419</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>136348934</v>
       </c>
       <c r="B19" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>136348935</v>
       </c>
       <c r="B20" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>136348940</v>
       </c>
       <c r="B21" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>136348939</v>
       </c>
       <c r="B22" t="n">
-        <v>93057</v>
+        <v>93059</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         <v>136348938</v>
       </c>
       <c r="B27" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
